--- a/docs/ValueSet-BRTipoObservacao-1.0.xlsx
+++ b/docs/ValueSet-BRTipoObservacao-1.0.xlsx
@@ -32,7 +32,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.0.0-release</t>
   </si>
   <si>
     <t>Name</t>
@@ -74,7 +74,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>null (http://www.saude.gov.br)</t>
+    <t>Ministério da Saúde do Brasil (http://www.saude.gov.br, cgiis.datasus@saude.gov.br)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -131,79 +131,79 @@
     <t>8665-2</t>
   </si>
   <si>
-    <t>Data da Última Menstruação</t>
+    <t>Last menstrual period start date</t>
   </si>
   <si>
     <t>56832-9</t>
   </si>
   <si>
-    <t>Exposição à Substâncias</t>
+    <t>Type of substance abused</t>
   </si>
   <si>
     <t>11996-6</t>
   </si>
   <si>
-    <t>Quantidade de Gestações</t>
+    <t>Pregnancies</t>
   </si>
   <si>
     <t>63895-7</t>
   </si>
   <si>
-    <t>Tipo de Aleitamento Materno</t>
+    <t>Breastfeeding status</t>
   </si>
   <si>
     <t>29463-7</t>
   </si>
   <si>
-    <t>Peso Corporal</t>
+    <t>Body weight</t>
   </si>
   <si>
     <t>8480-6</t>
   </si>
   <si>
-    <t>Pressão Arterial Sistólica</t>
+    <t>Systolic blood pressure</t>
   </si>
   <si>
     <t>8462-4</t>
   </si>
   <si>
-    <t>Pressão Arterial Diastólica</t>
+    <t>Diastolic blood pressure</t>
   </si>
   <si>
     <t>8280-0</t>
   </si>
   <si>
-    <t>Circuferência Abdominal</t>
+    <t>Waist Circumference at umbilicus by Tape measure</t>
   </si>
   <si>
     <t>9843-4</t>
   </si>
   <si>
-    <t>Perímetro Cefálico</t>
+    <t>Head Occipital-frontal circumference</t>
   </si>
   <si>
     <t>8302-2</t>
   </si>
   <si>
-    <t>Altura</t>
+    <t>Body height</t>
   </si>
   <si>
     <t>11885-1</t>
   </si>
   <si>
-    <t>Idade Gestacional</t>
+    <t>Gestational age Estimated from last menstrual period</t>
   </si>
   <si>
     <t>11612-9</t>
   </si>
   <si>
-    <t>Quantidade de Abortos</t>
+    <t>Abortions</t>
   </si>
   <si>
     <t>48767-8</t>
   </si>
   <si>
-    <t>Anotação de Comentário para Narrativa [Interpretação]</t>
+    <t>Annotation comment [Interpretation] Narrative</t>
   </si>
   <si>
     <t>http://loinc.org</t>
